--- a/data/trans_bre/IP25-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Provincia-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,8 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,15 +531,13 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Brecha de género relativa</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -563,27 +559,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -596,13 +582,11 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -627,27 +611,17 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-2,86%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-2,86%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
           <t>-4,52%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -660,49 +634,39 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 7,15</t>
+          <t>-12,16; 8,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 8,15</t>
+          <t>-6,61; 8,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 5,53</t>
+          <t>-14,39; 5,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,3; 9,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 8,56</t>
+          <t>-6,94; 9,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 9,24</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-15,07; 6,51</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-15,49; 6,9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -727,27 +691,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,58%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-0,58%</t>
+          <t>-4,75%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-4,75%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
           <t>-3,6%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -760,49 +714,39 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 6,57</t>
+          <t>-7,2; 7,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 2,75</t>
+          <t>-11,18; 3,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 0,85</t>
+          <t>-8,69; 1,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,88; 8,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 7,72</t>
+          <t>-12,27; 3,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 3,18</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-9,25; 0,89</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-8,86; 1,53</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -827,27 +771,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-2,2%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-2,2%</t>
+          <t>-2,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
           <t>1,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -860,42 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 5,07</t>
+          <t>-9,7; 4,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 4,46</t>
+          <t>-9,47; 4,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 10,85</t>
+          <t>-10,44; 10,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,14; 5,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 5,48</t>
+          <t>-9,77; 5,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 4,88</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-10,38; 13,6</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-11,84; 13,17</t>
         </is>
       </c>
     </row>
@@ -927,27 +851,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
           <t>-6,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -960,42 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 8,53</t>
+          <t>-5,08; 8,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 8,17</t>
+          <t>-6,53; 8,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 1,76</t>
+          <t>-13,74; 1,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,36; 10,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 9,59</t>
+          <t>-6,92; 10,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 9,69</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-15,23; 1,95</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-14,24; 2,02</t>
         </is>
       </c>
     </row>
@@ -1027,27 +931,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>-0,04%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,04%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
           <t>6,01%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +954,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 17,54</t>
+          <t>-11,28; 15,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 7,61</t>
+          <t>-7,47; 7,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 16,56</t>
+          <t>-4,89; 16,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,22; 22,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 25,51</t>
+          <t>-7,64; 7,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 8,3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-5,44; 20,95</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-5,48; 20,88</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,27 +1011,17 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>-1,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-1,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
           <t>-3,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1160,49 +1034,39 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 10,71</t>
+          <t>-5,51; 10,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 6,32</t>
+          <t>-10,51; 7,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 5,13</t>
+          <t>-11,58; 4,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,9; 12,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 12,78</t>
+          <t>-10,89; 8,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 7,03</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-11,98; 5,58</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-11,95; 5,0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1227,27 +1091,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>-4,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
           <t>3,38%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 11,62</t>
+          <t>-0,05; 11,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 2,59</t>
+          <t>-11,43; 2,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 8,54</t>
+          <t>-2,15; 9,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,08; 14,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 13,77</t>
+          <t>-12,39; 3,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 3,02</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-2,9; 9,87</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-2,36; 10,95</t>
         </is>
       </c>
     </row>
@@ -1327,27 +1171,17 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>-2,43%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-2,43%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
           <t>-3,76%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,78</t>
+          <t>1,35; 13,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 2,99</t>
+          <t>-7,15; 3,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 0,99</t>
+          <t>-8,47; 1,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,54; 16,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,78; 17,45</t>
+          <t>-7,63; 3,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 3,28</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-8,87; 1,1</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-8,97; 1,32</t>
         </is>
       </c>
     </row>
@@ -1427,27 +1251,17 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>-2,38%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,38%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
           <t>-1,64%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 5,65</t>
+          <t>0,28; 5,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 0,5</t>
+          <t>-4,65; 0,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 1,09</t>
+          <t>-4,04; 0,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,23; 6,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 6,52</t>
+          <t>-4,98; 0,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 0,55</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-4,17; 1,21</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-4,39; 1,03</t>
         </is>
       </c>
     </row>
@@ -1508,16 +1312,16 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
     <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A14:A15"/>
   </mergeCells>

--- a/data/trans_bre/IP25-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 8,24</t>
+          <t>-12,93; 7,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 8,44</t>
+          <t>-7,11; 8,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 5,92</t>
+          <t>-13,75; 6,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 9,8</t>
+          <t>-14,16; 9,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 9,67</t>
+          <t>-7,3; 9,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 6,9</t>
+          <t>-15,08; 7,35</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 7,05</t>
+          <t>-7,5; 6,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 3,02</t>
+          <t>-11,53; 3,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 1,44</t>
+          <t>-9,73; 0,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 8,47</t>
+          <t>-8,19; 8,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 3,5</t>
+          <t>-12,6; 3,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 1,53</t>
+          <t>-9,9; 0,78</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 4,72</t>
+          <t>-9,06; 4,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 4,53</t>
+          <t>-9,38; 4,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 10,64</t>
+          <t>-9,69; 10,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 5,17</t>
+          <t>-9,43; 5,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 5,03</t>
+          <t>-10,02; 5,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 13,17</t>
+          <t>-10,8; 13,75</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 8,94</t>
+          <t>-4,92; 9,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 8,99</t>
+          <t>-6,94; 8,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 1,97</t>
+          <t>-13,82; 1,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 10,27</t>
+          <t>-5,04; 10,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 10,49</t>
+          <t>-7,37; 9,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 2,02</t>
+          <t>-14,34; 1,85</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 15,68</t>
+          <t>-11,1; 17,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 7,22</t>
+          <t>-6,83; 7,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 16,28</t>
+          <t>-5,13; 16,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 22,64</t>
+          <t>-13,07; 24,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 7,98</t>
+          <t>-6,95; 7,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 20,88</t>
+          <t>-5,48; 21,75</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 10,4</t>
+          <t>-5,7; 10,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 7,37</t>
+          <t>-9,31; 7,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 4,55</t>
+          <t>-11,86; 4,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 12,13</t>
+          <t>-6,1; 12,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 8,44</t>
+          <t>-9,85; 8,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 5,0</t>
+          <t>-12,39; 4,94</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 11,94</t>
+          <t>0,09; 11,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 2,68</t>
+          <t>-11,1; 2,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 9,34</t>
+          <t>-2,42; 8,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 14,19</t>
+          <t>0,04; 13,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 3,17</t>
+          <t>-12,07; 2,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 10,95</t>
+          <t>-2,63; 9,72</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 13,41</t>
+          <t>0,36; 12,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 3,02</t>
+          <t>-7,65; 2,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 1,21</t>
+          <t>-8,52; 0,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,54; 16,96</t>
+          <t>0,49; 15,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 3,34</t>
+          <t>-8,05; 2,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 1,32</t>
+          <t>-8,97; 1,03</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 5,5</t>
+          <t>0,24; 5,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 0,54</t>
+          <t>-4,63; 0,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,93</t>
+          <t>-3,92; 1,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,4</t>
+          <t>0,31; 6,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 0,6</t>
+          <t>-5,01; 0,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,03</t>
+          <t>-4,27; 1,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP25-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 7,65</t>
+          <t>-12,28; 7,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 8,18</t>
+          <t>-7,33; 8,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 6,32</t>
+          <t>-13,85; 5,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 9,24</t>
+          <t>-13,08; 8,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 9,42</t>
+          <t>-7,66; 9,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 7,35</t>
+          <t>-15,07; 6,51</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 6,73</t>
+          <t>-8,6; 6,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 3,02</t>
+          <t>-11,52; 2,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 0,74</t>
+          <t>-8,92; 0,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 8,05</t>
+          <t>-9,37; 7,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 3,54</t>
+          <t>-12,39; 3,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 0,78</t>
+          <t>-9,25; 0,89</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 4,66</t>
+          <t>-9,49; 5,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 4,91</t>
+          <t>-10,06; 4,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 10,8</t>
+          <t>-9,15; 10,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 5,14</t>
+          <t>-9,92; 5,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 5,36</t>
+          <t>-10,38; 4,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 13,75</t>
+          <t>-10,38; 13,6</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 9,24</t>
+          <t>-4,86; 8,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 8,06</t>
+          <t>-7,42; 8,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 1,61</t>
+          <t>-14,62; 1,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 10,85</t>
+          <t>-5,11; 9,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 9,47</t>
+          <t>-7,79; 9,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 1,85</t>
+          <t>-15,23; 1,95</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 17,47</t>
+          <t>-11,08; 17,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 7,21</t>
+          <t>-6,81; 7,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 16,82</t>
+          <t>-5,07; 16,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 24,67</t>
+          <t>-13,04; 25,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 7,9</t>
+          <t>-7,0; 8,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 21,75</t>
+          <t>-5,44; 20,95</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 10,51</t>
+          <t>-6,34; 10,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 7,59</t>
+          <t>-10,6; 6,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 4,46</t>
+          <t>-11,52; 5,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 12,25</t>
+          <t>-6,43; 12,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 8,83</t>
+          <t>-10,87; 7,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 4,94</t>
+          <t>-11,98; 5,58</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 11,41</t>
+          <t>0,39; 11,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 2,01</t>
+          <t>-10,54; 2,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 8,41</t>
+          <t>-2,71; 8,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 13,51</t>
+          <t>0,45; 13,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 2,17</t>
+          <t>-11,46; 3,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 9,72</t>
+          <t>-2,9; 9,87</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 12,45</t>
+          <t>1,51; 13,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 2,64</t>
+          <t>-7,23; 2,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 0,95</t>
+          <t>-8,41; 0,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,49; 15,74</t>
+          <t>1,78; 17,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 2,98</t>
+          <t>-7,74; 3,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 1,03</t>
+          <t>-8,87; 1,1</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,24; 5,55</t>
+          <t>0,09; 5,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,41</t>
+          <t>-4,72; 0,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,03</t>
+          <t>-3,84; 1,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 6,48</t>
+          <t>0,1; 6,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,44</t>
+          <t>-5,12; 0,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 1,15</t>
+          <t>-4,17; 1,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP25-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Provincia-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,53</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,86%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-4,52%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.533262023334448</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.2707135523201454</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-3.999382987874311</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-0.02860725705129478</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.002912965356809326</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.04515341528995976</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-12,28; 7,15</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,33; 8,15</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-13,85; 5,53</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-13,08; 8,56</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-7,66; 9,24</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-15,07; 6,51</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-12.27537996967568</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.334265184249548</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-13.85305461466718</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.1307686589423954</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.07656376446190738</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1506574864071764</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.152761825072697</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.152102885190301</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.529438873801316</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.0856329409135356</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.09240854251789349</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.06507383117674144</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Cádiz</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-4,24</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-3,45</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,58%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-4,75%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-3,6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-8,6; 6,57</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-11,52; 2,75</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-8,92; 0,85</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-9,37; 7,72</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-12,39; 3,18</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-9,25; 0,89</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.5113160330245559</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-4.236502450562474</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-3.450140789758949</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.005812891401470384</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.0474750372796142</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.0359919814338619</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,06</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,37</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,2%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,52%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.604912619321164</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-11.52495371767444</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-8.924826755191521</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.09372623456163411</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1238773019622361</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.09246338423145684</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-9,49; 5,07</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-10,06; 4,46</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-9,15; 10,85</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-9,92; 5,48</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-10,38; 4,88</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-10,38; 13,6</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.571785812257172</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.747718437130377</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.8462585358111921</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.07723076455193963</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.031818203576152</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.00893031365758384</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +767,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,49</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-5,9</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-6,27%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.06459131699267</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.372155871349335</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.142639232030052</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.02202357559233316</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.02516844542576772</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.01357889421906346</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,86; 8,53</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-7,42; 8,17</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-14,62; 1,76</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-5,11; 9,59</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-7,79; 9,69</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-15,23; 1,95</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.49299918847843</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-10.06320234246524</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-9.145443090569467</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.09924838867617793</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1037735038806234</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1037621801799154</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Huelva</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.073376287937255</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.463056806674017</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10.85441761673521</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.05483011767885303</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.04880238153871501</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.13604284828969</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,09</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,19</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,04%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-11,08; 17,54</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-6,81; 7,61</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-5,07; 16,56</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-13,04; 25,51</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-7,0; 8,3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-5,44; 20,95</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>1.683088528294885</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4875714931341091</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-5.897857736906653</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.01832058675590973</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.005401484827218959</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.06272293986808526</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Jaén</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2,42</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-1,14</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-2,9</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-1,23%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-3,09%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.859011449741293</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-7.419690804591397</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-14.6196917864515</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.05107820342653404</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.07791015057586036</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1523486002048205</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-6,34; 10,71</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-10,6; 6,32</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-11,52; 5,13</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-6,43; 12,78</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-10,87; 7,03</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-11,98; 5,58</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>8.534250456172412</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8.168501507937902</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.760120059794905</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.09592524361313085</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.09688438476387949</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.01949661590554488</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,237 +931,407 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>5,7</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-4,03</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,02</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6,48%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-4,51%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>3.087933329805137</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.04224622613453466</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>5.186964617309919</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.03953589850381158</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.0004431125689703824</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.06007814974077173</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>0,39; 11,62</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-10,54; 2,59</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-2,71; 8,54</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0,45; 13,77</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-11,46; 3,02</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-2,9; 9,87</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-11.08073093702953</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-6.80878295201587</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-5.065384550098972</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.1304163902627038</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.06995773961732228</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.05438769747041332</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>17.54403187112291</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.60756021171921</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>16.55932960095855</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.2551302830472807</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.08302738268100583</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.2094857308878096</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>6,98</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-2,22</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-3,51</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-2,43%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-3,76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 13,78</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-7,23; 2,99</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-8,41; 0,99</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1,78; 17,45</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-7,74; 3,28</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-8,87; 1,1</t>
-        </is>
+      <c r="C19" s="5" t="n">
+        <v>2.419006353419728</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-1.137112731721801</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-2.902598010717006</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.02672812660321964</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.01234892638538804</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.03088963545430582</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>2,78</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-2,17</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,49</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,38%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-1,64%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-6.34278430483602</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-10.60432706042945</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-11.51833012628256</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.06431000912092928</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.1087431788373686</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.1197701061416485</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 5,65</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-4,72; 0,5</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-3,84; 1,09</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 6,52</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>-5,12; 0,55</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-4,17; 1,21</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>10.70602603228861</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>6.319205036919527</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>5.127951769419438</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.1277679987317686</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.07026667286335868</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.05582211358260253</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>5.698264724453129</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-4.028581078337378</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>3.017486075025755</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.06480739357551039</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.04512012718277981</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.03380318772569445</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0.3866790246699474</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-10.54152294389496</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-2.710846040038505</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0.004451415915054311</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.1146265205361515</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.02896517229784187</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>11.61799322240941</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2.592681549768541</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>8.539544230641935</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0.1377308366691858</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.03019266054880148</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.09866924351596883</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>6.980878000348156</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>-2.216975317236825</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>-3.509817152411421</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.08379648198400005</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.02425087232581458</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.03762852709450744</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>1.508597794243671</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>-7.23055610306237</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-8.405824020463319</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0.01775096819207253</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.07735012460343096</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.08872393547867088</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>13.77667752972665</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>2.989571316012497</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0.9935814738409114</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.1745191612749633</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.03282605668999405</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.01102102732089533</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>2.776740117313381</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-2.173199715805918</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-1.493617665982028</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>0.03172082477166212</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>-0.02381458875773705</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>-0.01635533306248851</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>0.08915016252287135</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-4.719499292334402</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-3.836271919237275</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0.0009667227748420159</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>-0.05121490315252061</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>-0.04166839330405903</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>5.647938539766834</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0.4989331690560716</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.086920194524964</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>0.06523975511321876</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0.005458926872619372</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>0.01207351016952813</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1313,17 +1340,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
